--- a/investigator/assets/AVAT 데이터 명세서.xlsx
+++ b/investigator/assets/AVAT 데이터 명세서.xlsx
@@ -1751,10 +1751,18 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="A96"/>
-      <c r="B96"/>
-    </row>
+    <ns0:row xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="96" spans="1:2">
+      <ns0:c r="A96" s="7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>report_accident_number</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B96" s="7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보고서 사고번호(날짜_순번)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
     <row r="97" spans="1:2">
       <c r="A97"/>
       <c r="B97"/>

--- a/investigator/assets/AVAT 데이터 명세서.xlsx
+++ b/investigator/assets/AVAT 데이터 명세서.xlsx
@@ -592,13 +592,13 @@
     <t>data_list_Other_Front_cam</t>
   </si>
   <si>
-    <t>기타 전방블랙박스 데이터 유무</t>
+    <t>타차 전방블랙박스 데이터 유무</t>
   </si>
   <si>
     <t>data_list_Other_Rear_cam</t>
   </si>
   <si>
-    <t>기타 후방블랙박스 데이터 유무</t>
+    <t>타차 후방블랙박스 데이터 유무</t>
   </si>
   <si>
     <t>data_list_Pedal_cam</t>
